--- a/Examples/HybridPowerSystem/Hybrid_4Bus/Hybrid_4Bus.xlsx
+++ b/Examples/HybridPowerSystem/Hybrid_4Bus/Hybrid_4Bus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Power-System-Analysis-Toolbox\Examples\HybridPowerSystem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gzhan\Documents\Imperial College London\PhD Year 1\Hybrid ACDC\Simplus-Grid-Tool-2025May_HybridACDC\Simplus-Grid-Tool\Examples\HybridPowerSystem\Hybrid_4Bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B47766-CD44-4283-B728-8E0B748B26A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5C3B04-08FD-4D9A-AA04-839849696A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28692" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -305,19 +305,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -326,7 +326,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -334,7 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -342,14 +342,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -378,7 +378,7 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -664,62 +664,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="4" max="4" width="9.46484375" customWidth="1"/>
-    <col min="6" max="6" width="10.9296875" customWidth="1"/>
-    <col min="9" max="9" width="10.73046875" customWidth="1"/>
-    <col min="10" max="10" width="11.1328125" customWidth="1"/>
-    <col min="11" max="11" width="10.1328125" customWidth="1"/>
-    <col min="12" max="12" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.90625" customWidth="1"/>
+    <col min="9" max="9" width="10.81640625" customWidth="1"/>
+    <col min="10" max="10" width="11.08984375" customWidth="1"/>
+    <col min="11" max="11" width="10.08984375" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12">
       <c r="A3" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12">
       <c r="A9" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
@@ -757,7 +757,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>1</v>
       </c>
@@ -795,7 +795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>3</v>
       </c>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>4</v>
       </c>
@@ -919,35 +919,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34645F5B-1D7A-4323-9AD6-5FF81941CA24}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.86328125" customWidth="1"/>
-    <col min="2" max="2" width="39.53125" customWidth="1"/>
+    <col min="1" max="1" width="9.90625" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15.265625" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" customWidth="1"/>
-    <col min="7" max="7" width="13.796875" customWidth="1"/>
-    <col min="8" max="8" width="15.1328125" customWidth="1"/>
-    <col min="9" max="9" width="18.73046875" customWidth="1"/>
-    <col min="10" max="10" width="18.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.1328125" customWidth="1"/>
-    <col min="12" max="12" width="17.9296875" customWidth="1"/>
-    <col min="13" max="13" width="14.46484375" customWidth="1"/>
-    <col min="14" max="14" width="13.1328125" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" customWidth="1"/>
+    <col min="12" max="12" width="17.90625" customWidth="1"/>
+    <col min="13" max="13" width="14.453125" customWidth="1"/>
+    <col min="14" max="14" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
@@ -958,7 +958,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>1</v>
       </c>
@@ -972,7 +972,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -986,7 +986,7 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1004,62 +1004,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D00B5E-E2E7-41B8-8388-8931D474EA96}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="7" max="7" width="12.3984375" customWidth="1"/>
+    <col min="7" max="7" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
@@ -1092,53 +1092,53 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0C2B6E-74BD-40FA-8EB6-D64D8C21837A}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.86328125" customWidth="1"/>
+    <col min="7" max="7" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1309,25 +1309,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB93A31-1E5A-4104-8C10-8E6599437516}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.54296875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1370,22 +1370,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFCB373-2341-40B6-A375-7BA50357479A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" customWidth="1"/>
+    <col min="1" max="1" width="30.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>47</v>
       </c>

--- a/Examples/HybridPowerSystem/Hybrid_4Bus/Hybrid_4Bus.xlsx
+++ b/Examples/HybridPowerSystem/Hybrid_4Bus/Hybrid_4Bus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gzhan\Documents\Imperial College London\PhD Year 1\Hybrid ACDC\Simplus-Grid-Tool-2025May_HybridACDC\Simplus-Grid-Tool\Examples\HybridPowerSystem\Hybrid_4Bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5C3B04-08FD-4D9A-AA04-839849696A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E41EF64D-F244-42AE-B991-0B0510511F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28692" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -664,14 +664,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.08984375" customWidth="1"/>
-    <col min="11" max="11" width="10.08984375" customWidth="1"/>
-    <col min="12" max="12" width="10.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -919,22 +919,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34645F5B-1D7A-4323-9AD6-5FF81941CA24}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.90625" customWidth="1"/>
-    <col min="2" max="2" width="39.54296875" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
-    <col min="8" max="8" width="15.08984375" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" customWidth="1"/>
-    <col min="10" max="10" width="18.54296875" customWidth="1"/>
-    <col min="11" max="11" width="17.08984375" customWidth="1"/>
-    <col min="12" max="12" width="17.90625" customWidth="1"/>
-    <col min="13" max="13" width="14.453125" customWidth="1"/>
-    <col min="14" max="14" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -963,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2"/>
       <c r="F4" s="2"/>
@@ -1004,9 +1004,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D00B5E-E2E7-41B8-8388-8931D474EA96}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1092,10 +1092,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0C2B6E-74BD-40FA-8EB6-D64D8C21837A}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.90625" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1309,12 +1309,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB93A31-1E5A-4104-8C10-8E6599437516}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1370,9 +1370,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFCB373-2341-40B6-A375-7BA50357479A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.08984375" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1439,7 +1439,7 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3">

--- a/Examples/HybridPowerSystem/Hybrid_4Bus/Hybrid_4Bus.xlsx
+++ b/Examples/HybridPowerSystem/Hybrid_4Bus/Hybrid_4Bus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Power-System-Analysis-Toolbox\Examples\HybridPowerSystem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gzhan\Documents\Imperial College London\PhD Year 1\Hybrid ACDC\Simplus-Grid-Tool-2025May_HybridACDC\Simplus-Grid-Tool\Examples\HybridPowerSystem\Hybrid_4Bus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B47766-CD44-4283-B728-8E0B748B26A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6951BBBA-1882-4ED4-9335-68947E697AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-72" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bus" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Advance" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -305,19 +306,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="164" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -326,7 +327,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -334,7 +335,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -342,14 +343,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -378,7 +379,7 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -664,62 +665,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="9.46484375" customWidth="1"/>
-    <col min="6" max="6" width="10.9296875" customWidth="1"/>
-    <col min="9" max="9" width="10.73046875" customWidth="1"/>
-    <col min="10" max="10" width="11.1328125" customWidth="1"/>
-    <col min="11" max="11" width="10.1328125" customWidth="1"/>
-    <col min="12" max="12" width="10.3984375" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.109375" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12">
       <c r="A1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12">
       <c r="A3" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12">
       <c r="A9" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
         <v>54</v>
       </c>
@@ -757,7 +758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12">
       <c r="A11">
         <v>1</v>
       </c>
@@ -777,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -795,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12">
       <c r="A12">
         <v>2</v>
       </c>
@@ -815,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -833,7 +834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12">
       <c r="A13">
         <v>3</v>
       </c>
@@ -853,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -871,7 +872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12">
       <c r="A14">
         <v>4</v>
       </c>
@@ -891,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -919,35 +920,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34645F5B-1D7A-4323-9AD6-5FF81941CA24}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.86328125" customWidth="1"/>
-    <col min="2" max="2" width="39.53125" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="15.265625" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" customWidth="1"/>
-    <col min="7" max="7" width="13.796875" customWidth="1"/>
-    <col min="8" max="8" width="15.1328125" customWidth="1"/>
-    <col min="9" max="9" width="18.73046875" customWidth="1"/>
-    <col min="10" max="10" width="18.59765625" customWidth="1"/>
-    <col min="11" max="11" width="17.1328125" customWidth="1"/>
-    <col min="12" max="12" width="17.9296875" customWidth="1"/>
-    <col min="13" max="13" width="14.46484375" customWidth="1"/>
-    <col min="14" max="14" width="13.1328125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" customWidth="1"/>
+    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="11" max="11" width="17.109375" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="14.44140625" customWidth="1"/>
+    <col min="14" max="14" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>54</v>
       </c>
@@ -958,7 +959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>1</v>
       </c>
@@ -972,7 +973,7 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -986,12 +987,12 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
   </sheetData>
@@ -1004,62 +1005,62 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D00B5E-E2E7-41B8-8388-8931D474EA96}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="7" max="7" width="12.3984375" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7">
       <c r="A10" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
@@ -1092,53 +1093,53 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0C2B6E-74BD-40FA-8EB6-D64D8C21837A}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="7" max="7" width="14.86328125" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7">
       <c r="A8" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7">
       <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
@@ -1161,7 +1162,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1</v>
       </c>
@@ -1184,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1207,7 +1208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1</v>
       </c>
@@ -1230,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>2</v>
       </c>
@@ -1253,7 +1254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1276,7 +1277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>4</v>
       </c>
@@ -1309,25 +1310,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EB93A31-1E5A-4104-8C10-8E6599437516}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1336,7 +1337,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1352,7 +1353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1370,22 +1371,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EFCB373-2341-40B6-A375-7BA50357479A}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" customWidth="1"/>
+    <col min="1" max="1" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -1394,7 +1395,7 @@
       </c>
       <c r="C3" s="3"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1402,7 +1403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -1410,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -1418,7 +1419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1426,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -1434,7 +1435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1442,7 +1443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1450,7 +1451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -1466,7 +1467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
